--- a/apps/web/public/Reverie_Import_Template.xlsx
+++ b/apps/web/public/Reverie_Import_Template.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:H4"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="2" max="2" width="28.83203125" customWidth="1"/>
@@ -408,6 +408,7 @@
     <col min="5" max="5" width="10.83203125" customWidth="1"/>
     <col min="6" max="6" width="10.83203125" customWidth="1"/>
     <col min="7" max="7" width="28.83203125" customWidth="1"/>
+    <col min="8" max="8" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -432,6 +433,9 @@
       <c r="G1" t="str">
         <v>Tags</v>
       </c>
+      <c r="H1" t="str">
+        <v>Owned</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -455,6 +459,9 @@
       <c r="G2" t="str">
         <v>fae, enemies-to-lovers</v>
       </c>
+      <c r="H2" t="str">
+        <v>Yes</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -478,6 +485,9 @@
       <c r="G3" t="str">
         <v>gothic, slow-burn</v>
       </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -501,17 +511,20 @@
       <c r="G4" t="str">
         <v>dragons, romantasy</v>
       </c>
+      <c r="H4" t="str">
+        <v>No</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H4"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A17"/>
   <cols>
     <col min="1" max="1" width="78.83203125" customWidth="1"/>
   </cols>
@@ -583,22 +596,27 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v/>
+        <v>• Owned — Yes or No. Blank counts as Yes; No marks a wishlist book (want it, don’t own it yet).</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>The three rows in “My Library” are examples — delete them and add your own.</v>
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
+        <v>The three rows in “My Library” are examples — delete them and add your own.</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
         <v>Re-importing is safe: Reverie matches and merges, it never makes duplicates.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A17"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/apps/web/public/Reverie_Import_Template.xlsx
+++ b/apps/web/public/Reverie_Import_Template.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="2" max="2" width="28.83203125" customWidth="1"/>
@@ -491,40 +491,66 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
+        <v>The Fine Print</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Lauren Asher</v>
+      </c>
+      <c r="C4" s="1" t="str">
+        <v>9781734070583</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Read</v>
+      </c>
+      <c r="E4" t="str">
+        <v>4</v>
+      </c>
+      <c r="F4" t="str">
+        <v>2025-01-12</v>
+      </c>
+      <c r="G4" t="str">
+        <v>billionaire, forced-proximity</v>
+      </c>
+      <c r="H4" t="str">
+        <v>Borrowed</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
         <v>Fourth Wing</v>
       </c>
-      <c r="B4" t="str">
+      <c r="B5" t="str">
         <v>Rebecca Yarros</v>
       </c>
-      <c r="C4" s="1" t="str">
+      <c r="C5" s="1" t="str">
         <v>9781649374042</v>
       </c>
-      <c r="D4" t="str">
+      <c r="D5" t="str">
         <v>Unread</v>
       </c>
-      <c r="E4" t="str">
+      <c r="E5" t="str">
         <v/>
       </c>
-      <c r="F4" t="str">
+      <c r="F5" t="str">
         <v/>
       </c>
-      <c r="G4" t="str">
+      <c r="G5" t="str">
         <v>dragons, romantasy</v>
       </c>
-      <c r="H4" t="str">
+      <c r="H5" t="str">
         <v>No</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H5"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A18"/>
   <cols>
     <col min="1" max="1" width="78.83203125" customWidth="1"/>
   </cols>
@@ -596,27 +622,32 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>• Owned — Yes or No. Blank counts as Yes; No marks a wishlist book (want it, don’t own it yet).</v>
+        <v>• Owned — Yes, Borrowed, or No. Blank counts as Yes; Borrowed = a copy you have on loan (a book</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v/>
+        <v xml:space="preserve">  in hand, just not yours to keep); No marks a wishlist book (want it, don’t own it yet).</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>The three rows in “My Library” are examples — delete them and add your own.</v>
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
+        <v>The rows in “My Library” are examples — delete them and add your own.</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
         <v>Re-importing is safe: Reverie matches and merges, it never makes duplicates.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A18"/>
   </ignoredErrors>
 </worksheet>
 </file>